--- a/StructureDefinition-ncpi-family-relationship.xlsx
+++ b/StructureDefinition-ncpi-family-relationship.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -510,7 +510,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -539,7 +539,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -622,7 +622,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -727,7 +727,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -818,7 +818,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -929,7 +929,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -988,7 +988,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1021,7 +1021,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1033,7 +1033,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1163,7 +1163,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1213,7 +1213,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1246,7 +1246,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1283,7 +1283,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1366,7 +1366,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1722,7 +1722,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1737,7 +1737,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-family-relationship.xlsx
+++ b/StructureDefinition-ncpi-family-relationship.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$37</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -81,6 +84,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>A relationship between individuals in a pedigree or family.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -102,13 +108,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Observation</t>
+    <t>FamilyMemberHistory</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://hl7.org/fhir/StructureDefinition/FamilyMemberHistory</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -234,9 +240,6 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: SNOMED CT Concept Domain Binding</t>
-  </si>
-  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -244,13 +247,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Vital Signs
-MeasurementResultsTests</t>
   </si>
   <si>
     <t>0</t>
@@ -263,32 +259,26 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
-  </si>
-  <si>
-    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+    <t>Information about patient's relatives, relevant for patient</t>
+  </si>
+  <si>
+    <t>Significant health conditions for a person related to the patient relevant in the context of care for the patient.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fhs-1:Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
-    <t>&lt; 363787002 |Observable entity|</t>
-  </si>
-  <si>
-    <t>OBX</t>
+    <t>Not in scope for v2</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>Observation.id</t>
+    <t>FamilyMemberHistory.id</t>
   </si>
   <si>
     <t>1</t>
@@ -313,7 +303,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>Observation.meta</t>
+    <t>FamilyMemberHistory.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -333,7 +323,7 @@
 </t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>FamilyMemberHistory.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -352,7 +342,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>Observation.language</t>
+    <t>FamilyMemberHistory.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -380,7 +370,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>Observation.text</t>
+    <t>FamilyMemberHistory.text</t>
   </si>
   <si>
     <t>narrative
@@ -406,7 +396,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>Observation.contained</t>
+    <t>FamilyMemberHistory.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -432,36 +422,64 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.extension</t>
+    <t>FamilyMemberHistory.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:relative</t>
+  </si>
+  <si>
+    <t>relative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {familymemberhistory-patient-record|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>The participant in the relationship who plays the role named by the relationship.</t>
+  </si>
+  <si>
+    <t>The participant in the relationship who plays the role named by the relationship.
+That is, if the relationship is `C96572` (**\"Biological Father\"**), the
+`relative` is the father and the `patient` is the child.
+This uses [the standard Patient Record extension](http://hl7.org/fhir/StructureDefinition/familymemberhistory-patient-record)
+for compatibility with the [GA4GH PedigreeRelationship profile](https://ga4gh.github.io/pedigree-fhir-ig/StructureDefinition-PedigreeRelationship.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -469,657 +487,437 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>Observation.identifier</t>
+    <t>FamilyMemberHistory.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this observation.</t>
-  </si>
-  <si>
-    <t>Allows observations to be distinguished and referenced.</t>
+    <t>External Id(s) for this record</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this family member history by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the family member history as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Observation.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfills
+    <t>FamilyMemberHistory.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
-  </si>
-  <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>The status of the result value.</t>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.status</t>
+  </si>
+  <si>
+    <t>partial | completed | entered-in-error | health-unknown</t>
+  </si>
+  <si>
+    <t>A code specifying the status of the record of the family history of a specific family member.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>A code that identifies the status of the family history record.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/history-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
-    <t>&lt; 445584004 |Report by finality status|</t>
-  </si>
-  <si>
-    <t>OBX-11</t>
-  </si>
-  <si>
-    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>Observation.category</t>
+    <t>FamilyMemberHistory.dataAbsentReason</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
+    <t>subject-unknown | withheld | unable-to-obtain | deferred</t>
+  </si>
+  <si>
+    <t>Describes why the family member's history is not available.</t>
+  </si>
+  <si>
+    <t>This is a separate element to allow it to have a distinct binding from reasonCode.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes describing the reason why a family member's history is not available.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/history-absent-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proband
 </t>
   </si>
   <si>
-    <t>The relationship between the subject and the target.</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The participant we are describing.</t>
+  </si>
+  <si>
+    <t>The participant we are describing.
+That is, if the relationship is `C96572` (**\"Biological Father\"**), the `patient` is the child
+and the `relative` is the father.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ].role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>When history was recorded or last updated</t>
+  </si>
+  <si>
+    <t>The date (and possibly time) when the family member history was recorded or last updated.</t>
+  </si>
+  <si>
+    <t>This should be captured even if the same as the date on the List aggregating the full family history.</t>
+  </si>
+  <si>
+    <t>Allows determination of how current the summary is.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>The family member described</t>
+  </si>
+  <si>
+    <t>This will either be a name or a description; e.g. "Aunt Susan", "my cousin with the red hair".</t>
+  </si>
+  <si>
+    <t>Allows greater ease in ensuring the same person is being talked about.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship</t>
+  </si>
+  <si>
+    <t>The role the relative fills with respect to the patient for this relationship.</t>
+  </si>
+  <si>
+    <t>The role the relative fills with respect to the patient for this relationship.
+`relative` is `relationship` to `patient`. For the sake of users,
+prefer to exclusively use `C96572`, `C96580`, and `ITWIN` for genetic relationships.
+All other genetic relationships can be expressed with these and inferred individuals.
+`ITWIN` should be used for all monozygotic multiples (triplets, quadruplets, etc.)
+and should be present for all the directions of the relationship.
+This provides an unambiguous representation of the genetic relationship
+that is easily convertable to and from
+[PED files](https://gatk.broadinstitute.org/hc/en-us/articles/360035531972-PED-Pedigree-format)</t>
+  </si>
+  <si>
+    <t># Examples
+## Example 1 (triplets):
+A,B,C are triplets. You need six `NcpiFamilyRelationship`
+resources:
+- A→B
+- B→A
+- A→C
+- C→A
+- B→C
+- C→B.
+## Example 2 (twins):
+If X and Y are twins, you need two `NcpiFamilyRelationship`
+resources:
+- X→Y
+- Y→X.
+## Example 3 (maternal grandchild):
+If Q is the maternal grandchild of the female R but Q's parent
+is outside the dataset, then you need to make an inferred Patient
+resource D and make two `NcpiFamilyRelationship` resources:
+- D-(Biological Mother)→Q
+- R-(Biological Mother)→D.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
+    <t>https://nih-ncpi.github.io/ncpi-fhir-ig-2/ValueSet/family-biological-relationship-vs</t>
   </si>
   <si>
     <t>code</t>
   </si>
   <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/ncpi-participant)
+    <t>FamilyMemberHistory.sex</t>
+  </si>
+  <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>The birth sex of the family member.</t>
+  </si>
+  <si>
+    <t>This element should ideally reflect whether the individual is genetically male or female.  However, as reported information based on the knowledge of the patient or reporting friend/relative, there may be situations where the reported sex might not be totally accurate.  E.g. 'Aunt Sue' might be XY rather than XX.  Questions soliciting this information should be phrased to encourage capture of genetic sex where known.  However, systems performing analysis should also allow for the possibility of imprecision with this element.</t>
+  </si>
+  <si>
+    <t>Not all relationship codes imply sex and the relative's sex can be relevant for risk assessments.</t>
+  </si>
+  <si>
+    <t>Codes describing the sex assigned at birth as documented on the birth registration.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.born[x]</t>
+  </si>
+  <si>
+    <t>Period
+datestring</t>
+  </si>
+  <si>
+    <t>(approximate) date of birth</t>
+  </si>
+  <si>
+    <t>The actual or approximate date of birth of the relative.</t>
+  </si>
+  <si>
+    <t>Allows calculation of the relative's age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhs-1
 </t>
   </si>
   <si>
-    <t>The participant we are describing</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t>The participant the subject has a relationship to, eg, 'Subject is Relationship to Target' or 'Subject is Mother of Target'</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
+    <t>player[classCode=LIV, determinerCode=INSTANCE]. birthDate (could be URG)</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.age[x]</t>
+  </si>
+  <si>
+    <t>Age
+Rangestring</t>
+  </si>
+  <si>
+    <t>(approximate) age</t>
+  </si>
+  <si>
+    <t>The age of the relative at the time the family member history is recorded.</t>
+  </si>
+  <si>
+    <t>use estimatedAge to indicate whether the age is actual or not.</t>
+  </si>
+  <si>
+    <t>While age can be calculated from date of birth, sometimes recording age directly is more natural for clinicians.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ].act[classCode=OBS,moodCode=EVN, code="age"].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.estimatedAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t>Age is estimated?</t>
+  </si>
+  <si>
+    <t>If true, indicates that the age value specified is an estimated value.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the fact that age is estimated can/should change the results of any algorithm that calculates based on the specified age.</t>
+  </si>
+  <si>
+    <t>Clinicians often prefer to specify an estimaged age rather than an age range.</t>
+  </si>
+  <si>
+    <t>It is unknown whether the age is an estimate or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhs-2
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
+    <t>FamilyMemberHistory.deceased[x]</t>
+  </si>
+  <si>
+    <t>boolean
+AgeRangedatestring</t>
+  </si>
+  <si>
+    <t>Dead? How old/when?</t>
+  </si>
+  <si>
+    <t>Deceased flag or the actual or approximate age of the relative at the time of death for the family member history record.</t>
+  </si>
+  <si>
+    <t>player[classCode=LIV, determinerCode=INSTANCE].deceasedInd, deceasedDate (could be URG)  For age, you'd hang an observation off the role</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.reasonCode</t>
+  </si>
+  <si>
+    <t>Why was family member history performed?</t>
+  </si>
+  <si>
+    <t>Describes why the family member history occurred in coded or textual form.</t>
+  </si>
+  <si>
+    <t>Textual reasons can be captured using reasonCode.text.</t>
+  </si>
+  <si>
+    <t>Codes indicating why the family member history was done.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|AllergyIntolerance|4.0.1|QuestionnaireResponse|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>&lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
-  </si>
-  <si>
-    <t>value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abnormal Flag
-</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values|</t>
-  </si>
-  <si>
-    <t>OBX-8</t>
-  </si>
-  <si>
-    <t>interpretationCode</t>
-  </si>
-  <si>
-    <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>Observation.note</t>
+    <t>Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
+  </si>
+  <si>
+    <t>Event.reasonReference</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.note</t>
   </si>
   <si>
     <t xml:space="preserve">Annotation
 </t>
   </si>
   <si>
-    <t>Comments about the observation</t>
-  </si>
-  <si>
-    <t>Comments about the observation or the results.</t>
-  </si>
-  <si>
-    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
-  </si>
-  <si>
-    <t>Need to be able to provide free text additional information.</t>
-  </si>
-  <si>
-    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
-  </si>
-  <si>
-    <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observed body part</t>
-  </si>
-  <si>
-    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 123037004 |Body structure|</t>
-  </si>
-  <si>
-    <t>OBX-20</t>
-  </si>
-  <si>
-    <t>targetSiteCode</t>
-  </si>
-  <si>
-    <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>How it was done</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
-  </si>
-  <si>
-    <t>OBX-17</t>
-  </si>
-  <si>
-    <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
-  </si>
-  <si>
-    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
-  </si>
-  <si>
-    <t>&lt; 123038009 |Specimen|</t>
-  </si>
-  <si>
-    <t>SPM segment</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SPC].specimen</t>
-  </si>
-  <si>
-    <t>704319004 |Inherent in|</t>
-  </si>
-  <si>
-    <t>Observation.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
-  </si>
-  <si>
-    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>&lt; 49062001 |Device|</t>
-  </si>
-  <si>
-    <t>OBX-17 / PRT -10</t>
-  </si>
-  <si>
-    <t>participation[typeCode=DEV]</t>
-  </si>
-  <si>
-    <t>424226004 |Using device|</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange</t>
+    <t>General note about related person</t>
+  </si>
+  <si>
+    <t>This property allows a non condition-specific note to the made about the related person. Ideally, the note would be in the condition property, but this is not always possible.</t>
+  </si>
+  <si>
+    <t>Event.note</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ANNGEN].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Provides guide for interpretation</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
-  </si>
-  <si>
-    <t>OBX.7</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
+    <t>Condition that the related person had</t>
+  </si>
+  <si>
+    <t>The significant Conditions (or condition) that the family member had. This is a repeating section to allow a system to represent more than one condition per resource, though there is nothing stopping multiple resources - one per condition.</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION, value&lt;Diagnosis]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.id</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -1134,7 +932,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.referenceRange.extension</t>
+    <t>FamilyMemberHistory.condition.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1143,7 +944,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.referenceRange.modifierExtension</t>
+    <t>FamilyMemberHistory.condition.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -1160,254 +961,77 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Observation.referenceRange.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
-</t>
-  </si>
-  <si>
-    <t>Low Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-3
-</t>
-  </si>
-  <si>
-    <t>OBX-7</t>
-  </si>
-  <si>
-    <t>value:IVL_PQ.low</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high</t>
-  </si>
-  <si>
-    <t>High Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
-  </si>
-  <si>
-    <t>value:IVL_PQ.high</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.type</t>
-  </si>
-  <si>
-    <t>Reference range qualifier</t>
-  </si>
-  <si>
-    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Code for the meaning of a reference range.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values| OR  -&lt; 365860008 |General clinical state finding| -OR -&lt; 250171008 |Clinical history or observation findings| OR  -&lt; 415229000 |Racial group| OR -&lt; 365400002 |Finding of puberty stage| OR-&lt; 443938003 |Procedure carried out on subject|</t>
-  </si>
-  <si>
-    <t>OBX-10</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo</t>
-  </si>
-  <si>
-    <t>Reference range population</t>
-  </si>
-  <si>
-    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Codes identifying the population the reference range applies to.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
-  </si>
-  <si>
-    <t>Applicable age range, if relevant</t>
-  </si>
-  <si>
-    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
-  </si>
-  <si>
-    <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.text</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
-  </si>
-  <si>
-    <t>value:ST</t>
-  </si>
-  <si>
-    <t>Observation.hasMember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
-  </si>
-  <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
-  </si>
-  <si>
-    <t>Relationships established by OBX-4 usage</t>
-  </si>
-  <si>
-    <t>outBoundRelationship</t>
-  </si>
-  <si>
-    <t>Observation.derivedFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
-  </si>
-  <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
-  </si>
-  <si>
-    <t>.targetObservation</t>
-  </si>
-  <si>
-    <t>Observation.component</t>
-  </si>
-  <si>
-    <t>Component results</t>
-  </si>
-  <si>
-    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
-  </si>
-  <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t>containment by OBX-4?</t>
-  </si>
-  <si>
-    <t>outBoundRelationship[typeCode=COMP]</t>
-  </si>
-  <si>
-    <t>Observation.component.id</t>
-  </si>
-  <si>
-    <t>Observation.component.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component.code</t>
-  </si>
-  <si>
-    <t>Type of component observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
-  </si>
-  <si>
-    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR -&lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]</t>
-  </si>
-  <si>
-    <t>Actual component result</t>
-  </si>
-  <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+    <t>FamilyMemberHistory.condition.code</t>
+  </si>
+  <si>
+    <t>Condition suffered by relation</t>
+  </si>
+  <si>
+    <t>The actual condition specified. Could be a coded condition (like MI or Diabetes) or a less specific string like 'cancer' depending on how much is known about the condition and the capabilities of the creating system.</t>
+  </si>
+  <si>
+    <t>Identification of the Condition or diagnosis.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+  </si>
+  <si>
+    <t>.value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.outcome</t>
+  </si>
+  <si>
+    <t>deceased | permanent disability | etc.</t>
+  </si>
+  <si>
+    <t>Indicates what happened following the condition.  If the condition resulted in death, deceased date is captured on the relation.</t>
+  </si>
+  <si>
+    <t>The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.contributedToDeath</t>
+  </si>
+  <si>
+    <t>Whether the condition contributed to the cause of death</t>
+  </si>
+  <si>
+    <t>This condition contributed to the cause of death of the related person. If contributedToDeath is not populated, then it is unknown.</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.onset[x]</t>
+  </si>
+  <si>
+    <t>Age
+RangePeriodstring</t>
+  </si>
+  <si>
+    <t>When condition first manifested</t>
+  </si>
+  <si>
+    <t>Either the age of onset, range of approximate age or descriptive string can be recorded.  For conditions with multiple occurrences, this describes the first known occurrence.</t>
+  </si>
+  <si>
+    <t>Age of onset of a condition in relatives is predictive of risk for the patient.</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="Subject Age at measurement", value&lt;Diagnosis].value[@xsi:typeCode='TS' or 'IVL_TS']  Use originalText for string</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.note</t>
+  </si>
+  <si>
+    <t>Extra information about condition</t>
+  </si>
+  <si>
+    <t>An area where general notes can be placed about this specific condition.</t>
   </si>
 </sst>
 </file>
@@ -1536,6 +1160,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1639,67 +1278,67 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1709,11 +1348,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1722,7 +1361,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="119.8046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1736,192 +1375,182 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.99609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>75</v>
-      </c>
-      <c r="AO1" t="s" s="1">
         <v>76</v>
       </c>
-      <c r="AP1" t="s" s="1">
-        <v>77</v>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>20</v>
@@ -1970,45 +1599,39 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" hidden="true">
+      <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2016,31 +1639,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2090,13 +1713,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2116,19 +1739,13 @@
       <c r="AN3" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP3" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2136,10 +1753,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2148,16 +1765,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2208,19 +1825,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2234,19 +1851,13 @@
       <c r="AN4" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP4" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2254,31 +1865,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2328,19 +1939,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2354,19 +1965,13 @@
       <c r="AN5" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO5" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP5" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2374,10 +1979,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2389,16 +1994,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2424,80 +2029,74 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP6" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2509,16 +2108,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2568,19 +2167,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2589,35 +2188,29 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2629,16 +2222,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2688,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2709,35 +2302,29 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2749,17 +2336,15 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2796,31 +2381,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2832,57 +2415,49 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2930,19 +2505,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2954,54 +2529,50 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3050,56 +2621,50 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AP11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3108,20 +2673,22 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3170,56 +2737,50 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3228,20 +2789,18 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3290,45 +2849,39 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3336,35 +2889,33 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3388,13 +2939,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3412,45 +2963,39 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3458,35 +3003,33 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3510,13 +3053,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3534,22 +3077,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3558,32 +3101,26 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3592,22 +3129,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3632,11 +3167,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3654,81 +3191,71 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3776,45 +3303,39 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3822,10 +3343,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3834,21 +3355,23 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3896,19 +3419,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3917,35 +3440,29 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3954,22 +3471,20 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4018,81 +3533,73 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4116,13 +3623,11 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4140,45 +3645,39 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4186,10 +3685,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4198,21 +3697,23 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4236,13 +3737,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4260,19 +3761,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4281,24 +3782,18 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4306,10 +3801,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4318,20 +3813,20 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4380,45 +3875,39 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4426,10 +3915,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4438,22 +3927,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4502,45 +3991,39 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4548,10 +4031,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4560,27 +4043,29 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4600,13 +4085,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4624,19 +4109,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4645,35 +4130,29 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4682,23 +4161,19 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4722,13 +4197,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4746,45 +4221,39 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4792,10 +4261,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4804,23 +4273,21 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4844,13 +4311,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4868,45 +4335,39 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4914,10 +4375,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4926,20 +4387,18 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4964,13 +4423,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4988,45 +4447,39 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>316</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5034,10 +4487,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5049,20 +4502,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5086,13 +4535,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5110,45 +4559,39 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5156,10 +4599,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5171,17 +4614,15 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5230,45 +4671,39 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5276,10 +4711,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5291,17 +4726,15 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5350,56 +4783,50 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5411,20 +4838,18 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>345</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5472,19 +4897,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>350</v>
+        <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5493,56 +4918,54 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>354</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5590,19 +5013,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5611,35 +5034,29 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5651,17 +5068,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>138</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5686,13 +5101,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5710,19 +5125,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5731,60 +5146,50 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5808,13 +5213,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5832,19 +5237,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5853,24 +5258,18 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5878,10 +5277,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5893,13 +5292,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>369</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>370</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5950,19 +5349,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5971,24 +5370,18 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5996,10 +5389,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6011,16 +5404,18 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>368</v>
+        <v>307</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6068,19 +5463,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6089,24 +5484,18 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>372</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6114,10 +5503,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6129,20 +5518,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6166,13 +5551,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>383</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6190,1732 +5575,52 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>386</v>
+        <v>271</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN37">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI36">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-ncpi-family-relationship.xlsx
+++ b/StructureDefinition-ncpi-family-relationship.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$37</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,9 +81,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A relationship between individuals in a pedigree or family.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -108,13 +102,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>FamilyMemberHistory</t>
+    <t>Observation</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/FamilyMemberHistory</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -240,6 +234,9 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: SNOMED CT Concept Domain Binding</t>
+  </si>
+  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -247,6 +244,13 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: SNOMED CT Attribute Binding</t>
+  </si>
+  <si>
+    <t>Vital Signs
+MeasurementResultsTests</t>
   </si>
   <si>
     <t>0</t>
@@ -259,26 +263,32 @@
 </t>
   </si>
   <si>
-    <t>Information about patient's relatives, relevant for patient</t>
-  </si>
-  <si>
-    <t>Significant health conditions for a person related to the patient relevant in the context of care for the patient.</t>
+    <t>Measurements and simple assertions</t>
+  </si>
+  <si>
+    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+  </si>
+  <si>
+    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fhs-1:Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
-    <t>Not in scope for v2</t>
+    <t>&lt; 363787002 |Observable entity|</t>
+  </si>
+  <si>
+    <t>OBX</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.id</t>
+    <t>Observation.id</t>
   </si>
   <si>
     <t>1</t>
@@ -303,7 +313,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.meta</t>
+    <t>Observation.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -323,7 +333,7 @@
 </t>
   </si>
   <si>
-    <t>FamilyMemberHistory.implicitRules</t>
+    <t>Observation.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -342,7 +352,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.language</t>
+    <t>Observation.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -370,7 +380,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.text</t>
+    <t>Observation.text</t>
   </si>
   <si>
     <t>narrative
@@ -396,7 +406,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.contained</t>
+    <t>Observation.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -422,24 +432,24 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.extension</t>
+    <t>Observation.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -449,35 +459,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.extension:relative</t>
-  </si>
-  <si>
-    <t>relative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {familymemberhistory-patient-record|4.0.1}
-</t>
-  </si>
-  <si>
-    <t>The participant in the relationship who plays the role named by the relationship.</t>
-  </si>
-  <si>
-    <t>The participant in the relationship who plays the role named by the relationship.
-That is, if the relationship is `C96572` (**\"Biological Father\"**), the
-`relative` is the father and the `patient` is the child.
-This uses [the standard Patient Record extension](http://hl7.org/fhir/StructureDefinition/familymemberhistory-patient-record)
-for compatibility with the [GA4GH PedigreeRelationship profile](https://ga4gh.github.io/pedigree-fhir-ig/StructureDefinition-PedigreeRelationship.html)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
+    <t>Observation.modifierExtension</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -487,439 +469,659 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.identifier</t>
+    <t>Observation.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>External Id(s) for this record</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this family member history by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the family member history as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>Business Identifier for observation</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this observation.</t>
+  </si>
+  <si>
+    <t>Allows observations to be distinguished and referenced.</t>
   </si>
   <si>
     <t>Event.identifier</t>
   </si>
   <si>
+    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
+    <t>Observation.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulfills
 </t>
   </si>
   <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.status</t>
-  </si>
-  <si>
-    <t>partial | completed | entered-in-error | health-unknown</t>
-  </si>
-  <si>
-    <t>A code specifying the status of the record of the family history of a specific family member.</t>
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Fulfills plan, proposal or order</t>
+  </si>
+  <si>
+    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+  </si>
+  <si>
+    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+  </si>
+  <si>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>registered | preliminary | final | amended +</t>
+  </si>
+  <si>
+    <t>The status of the result value.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
-    <t>A code that identifies the status of the family history record.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/history-status|4.0.1</t>
+    <t>Codes providing the status of an observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
+    <t>&lt; 445584004 |Report by finality status|</t>
+  </si>
+  <si>
+    <t>OBX-11</t>
+  </si>
+  <si>
+    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
+  </si>
+  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.dataAbsentReason</t>
+    <t>Observation.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>subject-unknown | withheld | unable-to-obtain | deferred</t>
-  </si>
-  <si>
-    <t>Describes why the family member's history is not available.</t>
-  </si>
-  <si>
-    <t>This is a separate element to allow it to have a distinct binding from reasonCode.</t>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
+    <t>The relationship between the subject and the target.</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/ncpi-participant)
+</t>
+  </si>
+  <si>
+    <t>The participant we are describing</t>
+  </si>
+  <si>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+  </si>
+  <si>
+    <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>participation[typeCode=RTGT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t>The participant the subject has a relationship to, eg, 'Subject is Relationship to Target' or 'Subject is Mother of Target'</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
+</t>
+  </si>
+  <si>
+    <t>dateTime
+PeriodTiminginstant</t>
+  </si>
+  <si>
+    <t>Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
+    <t>&lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>OBX.2, OBX.5, OBX.6</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+  </si>
+  <si>
+    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
+</t>
+  </si>
+  <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abnormal Flag
+</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+  </si>
+  <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the observation</t>
+  </si>
+  <si>
+    <t>Comments about the observation or the results.</t>
+  </si>
+  <si>
+    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
+  </si>
+  <si>
+    <t>Need to be able to provide free text additional information.</t>
+  </si>
+  <si>
+    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
+  </si>
+  <si>
+    <t>subjectOf.observationEvent[code="annotation"].value</t>
+  </si>
+  <si>
+    <t>Observation.bodySite</t>
+  </si>
+  <si>
+    <t>Observed body part</t>
+  </si>
+  <si>
+    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes describing the reason why a family member's history is not available.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/history-absent-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.patient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proband
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+  </si>
+  <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>How it was done</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>Methods for simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+  </si>
+  <si>
+    <t>OBX-17</t>
+  </si>
+  <si>
+    <t>methodCode</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
+    <t>Specimen used for this observation</t>
+  </si>
+  <si>
+    <t>The specimen that was used when this observation was made.</t>
+  </si>
+  <si>
+    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>&lt; 123038009 |Specimen|</t>
+  </si>
+  <si>
+    <t>SPM segment</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SPC].specimen</t>
+  </si>
+  <si>
+    <t>704319004 |Inherent in|</t>
+  </si>
+  <si>
+    <t>Observation.device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
-    <t>The participant we are describing.</t>
-  </si>
-  <si>
-    <t>The participant we are describing.
-That is, if the relationship is `C96572` (**\"Biological Father\"**), the `patient` is the child
-and the `relative` is the father.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ].role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>(Measurement) Device</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
+  </si>
+  <si>
+    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
+  </si>
+  <si>
+    <t>&lt; 49062001 |Device|</t>
+  </si>
+  <si>
+    <t>OBX-17 / PRT -10</t>
+  </si>
+  <si>
+    <t>participation[typeCode=DEV]</t>
+  </si>
+  <si>
+    <t>424226004 |Using device|</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>When history was recorded or last updated</t>
-  </si>
-  <si>
-    <t>The date (and possibly time) when the family member history was recorded or last updated.</t>
-  </si>
-  <si>
-    <t>This should be captured even if the same as the date on the List aggregating the full family history.</t>
-  </si>
-  <si>
-    <t>Allows determination of how current the summary is.</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.name</t>
+    <t>Provides guide for interpretation</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
+  </si>
+  <si>
+    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+  </si>
+  <si>
+    <t>OBX.7</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>The family member described</t>
-  </si>
-  <si>
-    <t>This will either be a name or a description; e.g. "Aunt Susan", "my cousin with the red hair".</t>
-  </si>
-  <si>
-    <t>Allows greater ease in ensuring the same person is being talked about.</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.relationship</t>
-  </si>
-  <si>
-    <t>The role the relative fills with respect to the patient for this relationship.</t>
-  </si>
-  <si>
-    <t>The role the relative fills with respect to the patient for this relationship.
-`relative` is `relationship` to `patient`. For the sake of users,
-prefer to exclusively use `C96572`, `C96580`, and `ITWIN` for genetic relationships.
-All other genetic relationships can be expressed with these and inferred individuals.
-`ITWIN` should be used for all monozygotic multiples (triplets, quadruplets, etc.)
-and should be present for all the directions of the relationship.
-This provides an unambiguous representation of the genetic relationship
-that is easily convertable to and from
-[PED files](https://gatk.broadinstitute.org/hc/en-us/articles/360035531972-PED-Pedigree-format)</t>
-  </si>
-  <si>
-    <t># Examples
-## Example 1 (triplets):
-A,B,C are triplets. You need six `NcpiFamilyRelationship`
-resources:
-- A→B
-- B→A
-- A→C
-- C→A
-- B→C
-- C→B.
-## Example 2 (twins):
-If X and Y are twins, you need two `NcpiFamilyRelationship`
-resources:
-- X→Y
-- Y→X.
-## Example 3 (maternal grandchild):
-If Q is the maternal grandchild of the female R but Q's parent
-is outside the dataset, then you need to make an inferred Patient
-resource D and make two `NcpiFamilyRelationship` resources:
-- D-(Biological Mother)→Q
-- R-(Biological Mother)→D.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://nih-ncpi.github.io/ncpi-fhir-ig-2/ValueSet/family-biological-relationship-vs</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.sex</t>
-  </si>
-  <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>The birth sex of the family member.</t>
-  </si>
-  <si>
-    <t>This element should ideally reflect whether the individual is genetically male or female.  However, as reported information based on the knowledge of the patient or reporting friend/relative, there may be situations where the reported sex might not be totally accurate.  E.g. 'Aunt Sue' might be XY rather than XX.  Questions soliciting this information should be phrased to encourage capture of genetic sex where known.  However, systems performing analysis should also allow for the possibility of imprecision with this element.</t>
-  </si>
-  <si>
-    <t>Not all relationship codes imply sex and the relative's sex can be relevant for risk assessments.</t>
-  </si>
-  <si>
-    <t>Codes describing the sex assigned at birth as documented on the birth registration.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.born[x]</t>
-  </si>
-  <si>
-    <t>Period
-datestring</t>
-  </si>
-  <si>
-    <t>(approximate) date of birth</t>
-  </si>
-  <si>
-    <t>The actual or approximate date of birth of the relative.</t>
-  </si>
-  <si>
-    <t>Allows calculation of the relative's age.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fhs-1
-</t>
-  </si>
-  <si>
-    <t>player[classCode=LIV, determinerCode=INSTANCE]. birthDate (could be URG)</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.age[x]</t>
-  </si>
-  <si>
-    <t>Age
-Rangestring</t>
-  </si>
-  <si>
-    <t>(approximate) age</t>
-  </si>
-  <si>
-    <t>The age of the relative at the time the family member history is recorded.</t>
-  </si>
-  <si>
-    <t>use estimatedAge to indicate whether the age is actual or not.</t>
-  </si>
-  <si>
-    <t>While age can be calculated from date of birth, sometimes recording age directly is more natural for clinicians.</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ].act[classCode=OBS,moodCode=EVN, code="age"].value</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.estimatedAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Age is estimated?</t>
-  </si>
-  <si>
-    <t>If true, indicates that the age value specified is an estimated value.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the fact that age is estimated can/should change the results of any algorithm that calculates based on the specified age.</t>
-  </si>
-  <si>
-    <t>Clinicians often prefer to specify an estimaged age rather than an age range.</t>
-  </si>
-  <si>
-    <t>It is unknown whether the age is an estimate or not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fhs-2
-</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.deceased[x]</t>
-  </si>
-  <si>
-    <t>boolean
-AgeRangedatestring</t>
-  </si>
-  <si>
-    <t>Dead? How old/when?</t>
-  </si>
-  <si>
-    <t>Deceased flag or the actual or approximate age of the relative at the time of death for the family member history record.</t>
-  </si>
-  <si>
-    <t>player[classCode=LIV, determinerCode=INSTANCE].deceasedInd, deceasedDate (could be URG)  For age, you'd hang an observation off the role</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.reasonCode</t>
-  </si>
-  <si>
-    <t>Why was family member history performed?</t>
-  </si>
-  <si>
-    <t>Describes why the family member history occurred in coded or textual form.</t>
-  </si>
-  <si>
-    <t>Textual reasons can be captured using reasonCode.text.</t>
-  </si>
-  <si>
-    <t>Codes indicating why the family member history was done.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|AllergyIntolerance|4.0.1|QuestionnaireResponse|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
-  </si>
-  <si>
-    <t>Event.reasonReference</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>General note about related person</t>
-  </si>
-  <si>
-    <t>This property allows a non condition-specific note to the made about the related person. Ideally, the note would be in the condition property, but this is not always possible.</t>
-  </si>
-  <si>
-    <t>Event.note</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ANNGEN].value</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Condition that the related person had</t>
-  </si>
-  <si>
-    <t>The significant Conditions (or condition) that the family member had. This is a repeating section to allow a system to represent more than one condition per resource, though there is nothing stopping multiple resources - one per condition.</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION, value&lt;Diagnosis]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.id</t>
-  </si>
-  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -932,10 +1134,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.condition.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
+    <t>Observation.referenceRange.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -944,7 +1143,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.condition.modifierExtension</t>
+    <t>Observation.referenceRange.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -961,77 +1160,254 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.condition.code</t>
-  </si>
-  <si>
-    <t>Condition suffered by relation</t>
-  </si>
-  <si>
-    <t>The actual condition specified. Could be a coded condition (like MI or Diabetes) or a less specific string like 'cancer' depending on how much is known about the condition and the capabilities of the creating system.</t>
-  </si>
-  <si>
-    <t>Identification of the Condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
-  </si>
-  <si>
-    <t>.value</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.outcome</t>
-  </si>
-  <si>
-    <t>deceased | permanent disability | etc.</t>
-  </si>
-  <si>
-    <t>Indicates what happened following the condition.  If the condition resulted in death, deceased date is captured on the relation.</t>
-  </si>
-  <si>
-    <t>The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-outcome|4.0.1</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.contributedToDeath</t>
-  </si>
-  <si>
-    <t>Whether the condition contributed to the cause of death</t>
-  </si>
-  <si>
-    <t>This condition contributed to the cause of death of the related person. If contributedToDeath is not populated, then it is unknown.</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.onset[x]</t>
-  </si>
-  <si>
-    <t>Age
-RangePeriodstring</t>
-  </si>
-  <si>
-    <t>When condition first manifested</t>
-  </si>
-  <si>
-    <t>Either the age of onset, range of approximate age or descriptive string can be recorded.  For conditions with multiple occurrences, this describes the first known occurrence.</t>
-  </si>
-  <si>
-    <t>Age of onset of a condition in relatives is predictive of risk for the patient.</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="Subject Age at measurement", value&lt;Diagnosis].value[@xsi:typeCode='TS' or 'IVL_TS']  Use originalText for string</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.note</t>
-  </si>
-  <si>
-    <t>Extra information about condition</t>
-  </si>
-  <si>
-    <t>An area where general notes can be placed about this specific condition.</t>
+    <t>Observation.referenceRange.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>Low Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-3
+</t>
+  </si>
+  <si>
+    <t>OBX-7</t>
+  </si>
+  <si>
+    <t>value:IVL_PQ.low</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.high</t>
+  </si>
+  <si>
+    <t>High Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
+  </si>
+  <si>
+    <t>value:IVL_PQ.high</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.type</t>
+  </si>
+  <si>
+    <t>Reference range qualifier</t>
+  </si>
+  <si>
+    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Code for the meaning of a reference range.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+  </si>
+  <si>
+    <t>&lt; 260245000 |Findings values| OR  +&lt; 365860008 |General clinical state finding| +OR +&lt; 250171008 |Clinical history or observation findings| OR  +&lt; 415229000 |Racial group| OR +&lt; 365400002 |Finding of puberty stage| OR+&lt; 443938003 |Procedure carried out on subject|</t>
+  </si>
+  <si>
+    <t>OBX-10</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>Reference range population</t>
+  </si>
+  <si>
+    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to identify the target population for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Applicable age range, if relevant</t>
+  </si>
+  <si>
+    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
+  </si>
+  <si>
+    <t>Some analytes vary greatly over age.</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.text</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
+  </si>
+  <si>
+    <t>value:ST</t>
+  </si>
+  <si>
+    <t>Observation.hasMember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Related resource that belongs to the Observation group</t>
+  </si>
+  <si>
+    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+  </si>
+  <si>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+  </si>
+  <si>
+    <t>Relationships established by OBX-4 usage</t>
+  </si>
+  <si>
+    <t>outBoundRelationship</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Related measurements the observation is made from</t>
+  </si>
+  <si>
+    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+  </si>
+  <si>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+  </si>
+  <si>
+    <t>.targetObservation</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
+  </si>
+  <si>
+    <t>Component results</t>
+  </si>
+  <si>
+    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
+  </si>
+  <si>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t>containment by OBX-4?</t>
+  </si>
+  <si>
+    <t>outBoundRelationship[typeCode=COMP]</t>
+  </si>
+  <si>
+    <t>Observation.component.id</t>
+  </si>
+  <si>
+    <t>Observation.component.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component.code</t>
+  </si>
+  <si>
+    <t>Type of component observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
+  </si>
+  <si>
+    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR +&lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Actual component result</t>
+  </si>
+  <si>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
   </si>
 </sst>
 </file>
@@ -1160,21 +1536,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1278,67 +1639,67 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1348,11 +1709,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1361,7 +1722,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="119.8046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1375,162 +1736,170 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.55078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.99609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AL1" t="s" s="1">
+      <c r="AM1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AM1" t="s" s="1">
+      <c r="AN1" t="s" s="1">
         <v>75</v>
       </c>
-      <c r="AN1" t="s" s="1">
+      <c r="AO1" t="s" s="1">
         <v>76</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>77</v>
+      </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1542,15 +1911,17 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>20</v>
@@ -1599,39 +1970,45 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AO2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1639,10 +2016,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1651,19 +2028,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1713,13 +2090,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1739,13 +2116,19 @@
       <c r="AN3" t="s" s="2">
         <v>20</v>
       </c>
+      <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1753,10 +2136,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1765,16 +2148,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1825,19 +2208,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1851,13 +2234,19 @@
       <c r="AN4" t="s" s="2">
         <v>20</v>
       </c>
+      <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1865,31 +2254,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1939,19 +2328,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1965,13 +2354,19 @@
       <c r="AN5" t="s" s="2">
         <v>20</v>
       </c>
+      <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1979,10 +2374,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1994,16 +2389,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2029,13 +2424,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2053,19 +2448,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2079,24 +2474,30 @@
       <c r="AN6" t="s" s="2">
         <v>20</v>
       </c>
+      <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2108,16 +2509,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2167,19 +2568,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2188,29 +2589,35 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2222,16 +2629,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2281,13 +2688,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2302,29 +2709,35 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2336,15 +2749,17 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2381,29 +2796,31 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2415,49 +2832,57 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2505,19 +2930,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2529,50 +2954,54 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2621,50 +3050,56 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2673,22 +3108,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2737,50 +3170,56 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2789,18 +3228,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2849,39 +3290,45 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2889,33 +3336,35 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2939,13 +3388,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2963,39 +3412,45 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3003,33 +3458,35 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3053,13 +3510,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3077,22 +3534,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3101,26 +3558,32 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>196</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3129,20 +3592,22 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O16" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3167,13 +3632,11 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3191,71 +3654,81 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>20</v>
+        <v>209</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3303,39 +3776,45 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3343,10 +3822,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3355,23 +3834,21 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3419,19 +3896,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3440,29 +3917,35 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>226</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3471,20 +3954,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3533,73 +4018,81 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -3623,11 +4116,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3645,39 +4140,45 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3685,10 +4186,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3697,23 +4198,21 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3737,13 +4236,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3761,19 +4260,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -3782,18 +4281,24 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3801,10 +4306,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3813,20 +4318,20 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3875,39 +4380,45 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3915,10 +4426,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3927,22 +4438,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3991,39 +4502,45 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>276</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4031,10 +4548,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4043,29 +4560,27 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q24" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4085,13 +4600,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4109,19 +4624,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4130,29 +4645,35 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4161,19 +4682,23 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4197,13 +4722,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4221,39 +4746,45 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>297</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4261,10 +4792,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4273,21 +4804,23 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4311,13 +4844,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4335,39 +4868,45 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>305</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4375,10 +4914,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4387,18 +4926,20 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4423,13 +4964,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4447,39 +4988,45 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>260</v>
+        <v>315</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>316</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4487,10 +5034,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4502,16 +5049,20 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4535,13 +5086,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -4559,39 +5110,45 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4599,10 +5156,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4614,15 +5171,17 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4671,39 +5230,45 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>334</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4711,10 +5276,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4726,15 +5291,17 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -4783,50 +5350,56 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>335</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>343</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4838,18 +5411,20 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>345</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -4897,19 +5472,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -4918,54 +5493,56 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>351</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>355</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5013,19 +5590,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>357</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5034,29 +5611,35 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5068,15 +5651,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5101,13 +5686,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5125,19 +5710,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>361</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5146,50 +5731,60 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5213,13 +5808,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5237,19 +5832,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5258,18 +5853,24 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5277,10 +5878,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5292,13 +5893,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>368</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5349,19 +5950,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5370,18 +5971,24 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5389,10 +5996,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5404,18 +6011,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5463,19 +6068,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5484,18 +6089,24 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>372</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5503,10 +6114,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5518,16 +6129,20 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5551,13 +6166,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>384</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5575,52 +6190,1732 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN37">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-ncpi-family-relationship.xlsx
+++ b/StructureDefinition-ncpi-family-relationship.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-family-relationship.xlsx
+++ b/StructureDefinition-ncpi-family-relationship.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$37</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,6 +84,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>A relationship between individuals in a pedigree or family.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -102,13 +108,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Observation</t>
+    <t>FamilyMemberHistory</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://purl.org/ga4gh/pedigree-fhir-ig/StructureDefinition/PedigreeRelationship</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -234,9 +240,6 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: SNOMED CT Concept Domain Binding</t>
-  </si>
-  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -244,13 +247,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Vital Signs
-MeasurementResultsTests</t>
   </si>
   <si>
     <t>0</t>
@@ -263,32 +259,26 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
-  </si>
-  <si>
-    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+    <t>Information about patient's relatives, relevant for patient</t>
+  </si>
+  <si>
+    <t>Significant health conditions for a person related to the patient relevant in the context of care for the patient.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fhs-1:Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
-    <t>&lt; 363787002 |Observable entity|</t>
-  </si>
-  <si>
-    <t>OBX</t>
+    <t>Not in scope for v2</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>Observation.id</t>
+    <t>FamilyMemberHistory.id</t>
   </si>
   <si>
     <t>1</t>
@@ -313,7 +303,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>Observation.meta</t>
+    <t>FamilyMemberHistory.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -333,7 +323,7 @@
 </t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>FamilyMemberHistory.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -352,7 +342,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>Observation.language</t>
+    <t>FamilyMemberHistory.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -374,13 +364,13 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
   </si>
   <si>
-    <t>Observation.text</t>
+    <t>FamilyMemberHistory.text</t>
   </si>
   <si>
     <t>narrative
@@ -406,7 +396,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>Observation.contained</t>
+    <t>FamilyMemberHistory.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -432,36 +422,64 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.extension</t>
+    <t>FamilyMemberHistory.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:relative</t>
+  </si>
+  <si>
+    <t>relative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {familymemberhistory-patient-record}
+</t>
+  </si>
+  <si>
+    <t>The participant in the relationship who plays the role named by the relationship.</t>
+  </si>
+  <si>
+    <t>The participant in the relationship who plays the role named by the relationship.
+That is, if the relationship is `KIN:028` (**\"isBiologicalFatherOf\"**), the
+`relative` is the father and the `patient` is the child.
+This uses [the standard Patient Record extension](http://hl7.org/fhir/StructureDefinition/familymemberhistory-patient-record)
+inherited from the [GA4GH PedigreeRelationship profile](https://ga4gh.github.io/pedigree-fhir-ig/StructureDefinition-PedigreeRelationship.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -469,657 +487,445 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>Observation.identifier</t>
+    <t>FamilyMemberHistory.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this observation.</t>
-  </si>
-  <si>
-    <t>Allows observations to be distinguished and referenced.</t>
+    <t>External Id(s) for this record</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this family member history by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the family member history as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Observation.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfills
+    <t>FamilyMemberHistory.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|ActivityDefinition|Measure|OperationDefinition)
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
-  </si>
-  <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>The status of the result value.</t>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.status</t>
+  </si>
+  <si>
+    <t>partial | completed | entered-in-error | health-unknown</t>
+  </si>
+  <si>
+    <t>A code specifying the status of the record of the family history of a specific family member.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>A code that identifies the status of the family history record.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/history-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
-    <t>&lt; 445584004 |Report by finality status|</t>
-  </si>
-  <si>
-    <t>OBX-11</t>
-  </si>
-  <si>
-    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>Observation.category</t>
+    <t>FamilyMemberHistory.dataAbsentReason</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
+    <t>subject-unknown | withheld | unable-to-obtain | deferred</t>
+  </si>
+  <si>
+    <t>Describes why the family member's history is not available.</t>
+  </si>
+  <si>
+    <t>This is a separate element to allow it to have a distinct binding from reasonCode.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes describing the reason why a family member's history is not available.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/history-absent-reason</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proband
 </t>
   </si>
   <si>
-    <t>The relationship between the subject and the target.</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+    <t xml:space="preserve">Reference(Patient)
+</t>
+  </si>
+  <si>
+    <t>The participant we are describing.</t>
+  </si>
+  <si>
+    <t>The participant we are describing.
+That is, if the relationship is `KIN:028` (**\"isBiologicalFatherOf\"**), the `patient` is the child
+and the `relative` is the father.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ].role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>When history was recorded or last updated</t>
+  </si>
+  <si>
+    <t>The date (and possibly time) when the family member history was recorded or last updated.</t>
+  </si>
+  <si>
+    <t>This should be captured even if the same as the date on the List aggregating the full family history.</t>
+  </si>
+  <si>
+    <t>Allows determination of how current the summary is.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>The family member described</t>
+  </si>
+  <si>
+    <t>This will either be a name or a description; e.g. "Aunt Susan", "my cousin with the red hair".</t>
+  </si>
+  <si>
+    <t>Allows greater ease in ensuring the same person is being talked about.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.relationship</t>
+  </si>
+  <si>
+    <t>The role the relative fills with respect to the patient for this relationship.</t>
+  </si>
+  <si>
+    <t>The role the relative fills with respect to the patient for this relationship.
+`relative` is `relationship` to `patient`.
+# NCPI-Recommended Codes
+For maximum interoperability with other NCPI systems, prefer these three codes for
+genetic relationships in [PED files](https://gatk.broadinstitute.org/hc/en-us/articles/360035531972-PED-Pedigree-format):
+- `KIN:027` (`isBiologicalMotherOf`): The relative is the biological mother of the patient.
+- `KIN:028` (`isBiologicalFatherOf`): The relative is the biological father of the patient.
+- `KIN:010` (`isMonozygoticMultipleBirthSiblingOf`): The relative and patient are monozygotic twins. For
+  higher-order multiples (triplets, quadruplets, etc.), create pairwise `KIN:010`
+  relationships between every pair with bidirectional relationships (both A→B and B→A).
+All other genetic relationships (grandparents, aunts, uncles, cousins, etc.) can be
+expressed using these three codes with inferred individuals to represent the relationship
+chain. This provides a canonical way to express all pedigree relationships, which will ease
+consuming the data.
+# Additional KIN Codes
+While all 55 codes from the [GA4GH KIN ontology](https://ga4gh.github.io/pedigree-fhir-ig/CodeSystem-kin.html)
+are available, NCPI systems may not fully support relationships beyond the three core codes above.</t>
+  </si>
+  <si>
+    <t># Examples
+## Example 1 (triplets):
+A,B,C are triplets. You need six `NcpiFamilyRelationship`
+resources with `KIN:010` (`isMonozygoticMultipleBirthSiblingOf`):
+- A→B
+- B→A
+- A→C
+- C→A
+- B→C
+- C→B.
+## Example 2 (twins):
+If X and Y are twins, you need two `NcpiFamilyRelationship`
+resources with `KIN:010` (`isMonozygoticMultipleBirthSiblingOf`):
+- X→Y
+- Y→X.
+## Example 3 (maternal grandchild):
+If Q is the maternal grandchild of the female R but Q's parent
+is outside the dataset, then you need to make an inferred Patient
+resource D and make two `NcpiFamilyRelationship` resources:
+- D-(KIN:027, `isBiologicalMotherOf`)→Q
+- R-(KIN:027, `isBiologicalMotherOf`)→D.</t>
+  </si>
+  <si>
+    <t>https://nih-ncpi.github.io/ncpi-fhir-ig-2/ValueSet/family-biological-relationship-vs</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.sex</t>
+  </si>
+  <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>The birth sex of the family member.</t>
+  </si>
+  <si>
+    <t>This element should ideally reflect whether the individual is genetically male or female.  However, as reported information based on the knowledge of the patient or reporting friend/relative, there may be situations where the reported sex might not be totally accurate.  E.g. 'Aunt Sue' might be XY rather than XX.  Questions soliciting this information should be phrased to encourage capture of genetic sex where known.  However, systems performing analysis should also allow for the possibility of imprecision with this element.</t>
+  </si>
+  <si>
+    <t>Not all relationship codes imply sex and the relative's sex can be relevant for risk assessments.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/ncpi-participant)
+    <t>Codes describing the sex assigned at birth as documented on the birth registration.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.born[x]</t>
+  </si>
+  <si>
+    <t>Period
+datestring</t>
+  </si>
+  <si>
+    <t>(approximate) date of birth</t>
+  </si>
+  <si>
+    <t>The actual or approximate date of birth of the relative.</t>
+  </si>
+  <si>
+    <t>Allows calculation of the relative's age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhs-1
 </t>
   </si>
   <si>
-    <t>The participant we are describing</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t>The participant the subject has a relationship to, eg, 'Subject is Relationship to Target' or 'Subject is Mother of Target'</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
+    <t>player[classCode=LIV, determinerCode=INSTANCE]. birthDate (could be URG)</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.age[x]</t>
+  </si>
+  <si>
+    <t>Age
+Rangestring</t>
+  </si>
+  <si>
+    <t>(approximate) age</t>
+  </si>
+  <si>
+    <t>The age of the relative at the time the family member history is recorded.</t>
+  </si>
+  <si>
+    <t>use estimatedAge to indicate whether the age is actual or not.</t>
+  </si>
+  <si>
+    <t>While age can be calculated from date of birth, sometimes recording age directly is more natural for clinicians.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ].act[classCode=OBS,moodCode=EVN, code="age"].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.estimatedAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t>Age is estimated?</t>
+  </si>
+  <si>
+    <t>If true, indicates that the age value specified is an estimated value.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the fact that age is estimated can/should change the results of any algorithm that calculates based on the specified age.</t>
+  </si>
+  <si>
+    <t>Clinicians often prefer to specify an estimaged age rather than an age range.</t>
+  </si>
+  <si>
+    <t>It is unknown whether the age is an estimate or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhs-2
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
+    <t>FamilyMemberHistory.deceased[x]</t>
+  </si>
+  <si>
+    <t>boolean
+AgeRangedatestring</t>
+  </si>
+  <si>
+    <t>Dead? How old/when?</t>
+  </si>
+  <si>
+    <t>Deceased flag or the actual or approximate age of the relative at the time of death for the family member history record.</t>
+  </si>
+  <si>
+    <t>player[classCode=LIV, determinerCode=INSTANCE].deceasedInd, deceasedDate (could be URG)  For age, you'd hang an observation off the role</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.reasonCode</t>
+  </si>
+  <si>
+    <t>Why was family member history performed?</t>
+  </si>
+  <si>
+    <t>Describes why the family member history occurred in coded or textual form.</t>
+  </si>
+  <si>
+    <t>Textual reasons can be captured using reasonCode.text.</t>
+  </si>
+  <si>
+    <t>Codes indicating why the family member history was done.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+  </si>
+  <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|Observation|AllergyIntolerance|QuestionnaireResponse|DiagnosticReport|DocumentReference)
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>&lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
-  </si>
-  <si>
-    <t>value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Observation.interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abnormal Flag
-</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values|</t>
-  </si>
-  <si>
-    <t>OBX-8</t>
-  </si>
-  <si>
-    <t>interpretationCode</t>
-  </si>
-  <si>
-    <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>Observation.note</t>
+    <t>Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
+  </si>
+  <si>
+    <t>Event.reasonReference</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.note</t>
   </si>
   <si>
     <t xml:space="preserve">Annotation
 </t>
   </si>
   <si>
-    <t>Comments about the observation</t>
-  </si>
-  <si>
-    <t>Comments about the observation or the results.</t>
-  </si>
-  <si>
-    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
-  </si>
-  <si>
-    <t>Need to be able to provide free text additional information.</t>
-  </si>
-  <si>
-    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
-  </si>
-  <si>
-    <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observed body part</t>
-  </si>
-  <si>
-    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 123037004 |Body structure|</t>
-  </si>
-  <si>
-    <t>OBX-20</t>
-  </si>
-  <si>
-    <t>targetSiteCode</t>
-  </si>
-  <si>
-    <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>How it was done</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
-  </si>
-  <si>
-    <t>OBX-17</t>
-  </si>
-  <si>
-    <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
-  </si>
-  <si>
-    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
-  </si>
-  <si>
-    <t>&lt; 123038009 |Specimen|</t>
-  </si>
-  <si>
-    <t>SPM segment</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SPC].specimen</t>
-  </si>
-  <si>
-    <t>704319004 |Inherent in|</t>
-  </si>
-  <si>
-    <t>Observation.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
-  </si>
-  <si>
-    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>&lt; 49062001 |Device|</t>
-  </si>
-  <si>
-    <t>OBX-17 / PRT -10</t>
-  </si>
-  <si>
-    <t>participation[typeCode=DEV]</t>
-  </si>
-  <si>
-    <t>424226004 |Using device|</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange</t>
+    <t>General note about related person</t>
+  </si>
+  <si>
+    <t>This property allows a non condition-specific note to the made about the related person. Ideally, the note would be in the condition property, but this is not always possible.</t>
+  </si>
+  <si>
+    <t>Event.note</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ANNGEN].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Provides guide for interpretation</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
-  </si>
-  <si>
-    <t>OBX.7</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
+    <t>Condition that the related person had</t>
+  </si>
+  <si>
+    <t>The significant Conditions (or condition) that the family member had. This is a repeating section to allow a system to represent more than one condition per resource, though there is nothing stopping multiple resources - one per condition.</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION, value&lt;Diagnosis]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.id</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -1134,7 +940,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.referenceRange.extension</t>
+    <t>FamilyMemberHistory.condition.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1143,7 +952,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.referenceRange.modifierExtension</t>
+    <t>FamilyMemberHistory.condition.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -1160,254 +969,77 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Observation.referenceRange.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
-</t>
-  </si>
-  <si>
-    <t>Low Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-3
-</t>
-  </si>
-  <si>
-    <t>OBX-7</t>
-  </si>
-  <si>
-    <t>value:IVL_PQ.low</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high</t>
-  </si>
-  <si>
-    <t>High Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
-  </si>
-  <si>
-    <t>value:IVL_PQ.high</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.type</t>
-  </si>
-  <si>
-    <t>Reference range qualifier</t>
-  </si>
-  <si>
-    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Code for the meaning of a reference range.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values| OR  -&lt; 365860008 |General clinical state finding| -OR -&lt; 250171008 |Clinical history or observation findings| OR  -&lt; 415229000 |Racial group| OR -&lt; 365400002 |Finding of puberty stage| OR-&lt; 443938003 |Procedure carried out on subject|</t>
-  </si>
-  <si>
-    <t>OBX-10</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo</t>
-  </si>
-  <si>
-    <t>Reference range population</t>
-  </si>
-  <si>
-    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Codes identifying the population the reference range applies to.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
-  </si>
-  <si>
-    <t>Applicable age range, if relevant</t>
-  </si>
-  <si>
-    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
-  </si>
-  <si>
-    <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.text</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
-  </si>
-  <si>
-    <t>value:ST</t>
-  </si>
-  <si>
-    <t>Observation.hasMember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
-  </si>
-  <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
-  </si>
-  <si>
-    <t>Relationships established by OBX-4 usage</t>
-  </si>
-  <si>
-    <t>outBoundRelationship</t>
-  </si>
-  <si>
-    <t>Observation.derivedFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
-  </si>
-  <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
-  </si>
-  <si>
-    <t>.targetObservation</t>
-  </si>
-  <si>
-    <t>Observation.component</t>
-  </si>
-  <si>
-    <t>Component results</t>
-  </si>
-  <si>
-    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
-  </si>
-  <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t>containment by OBX-4?</t>
-  </si>
-  <si>
-    <t>outBoundRelationship[typeCode=COMP]</t>
-  </si>
-  <si>
-    <t>Observation.component.id</t>
-  </si>
-  <si>
-    <t>Observation.component.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component.code</t>
-  </si>
-  <si>
-    <t>Type of component observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
-  </si>
-  <si>
-    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR -&lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]</t>
-  </si>
-  <si>
-    <t>Actual component result</t>
-  </si>
-  <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+    <t>FamilyMemberHistory.condition.code</t>
+  </si>
+  <si>
+    <t>Condition suffered by relation</t>
+  </si>
+  <si>
+    <t>The actual condition specified. Could be a coded condition (like MI or Diabetes) or a less specific string like 'cancer' depending on how much is known about the condition and the capabilities of the creating system.</t>
+  </si>
+  <si>
+    <t>Identification of the Condition or diagnosis.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+  </si>
+  <si>
+    <t>.value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.outcome</t>
+  </si>
+  <si>
+    <t>deceased | permanent disability | etc.</t>
+  </si>
+  <si>
+    <t>Indicates what happened following the condition.  If the condition resulted in death, deceased date is captured on the relation.</t>
+  </si>
+  <si>
+    <t>The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-outcome</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.contributedToDeath</t>
+  </si>
+  <si>
+    <t>Whether the condition contributed to the cause of death</t>
+  </si>
+  <si>
+    <t>This condition contributed to the cause of death of the related person. If contributedToDeath is not populated, then it is unknown.</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.onset[x]</t>
+  </si>
+  <si>
+    <t>Age
+RangePeriodstring</t>
+  </si>
+  <si>
+    <t>When condition first manifested</t>
+  </si>
+  <si>
+    <t>Either the age of onset, range of approximate age or descriptive string can be recorded.  For conditions with multiple occurrences, this describes the first known occurrence.</t>
+  </si>
+  <si>
+    <t>Age of onset of a condition in relatives is predictive of risk for the patient.</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="Subject Age at measurement", value&lt;Diagnosis].value[@xsi:typeCode='TS' or 'IVL_TS']  Use originalText for string</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.note</t>
+  </si>
+  <si>
+    <t>Extra information about condition</t>
+  </si>
+  <si>
+    <t>An area where general notes can be placed about this specific condition.</t>
   </si>
 </sst>
 </file>
@@ -1536,6 +1168,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1639,67 +1286,67 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1709,11 +1356,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1722,7 +1369,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.6328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1736,192 +1383,182 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.99609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>75</v>
-      </c>
-      <c r="AO1" t="s" s="1">
         <v>76</v>
       </c>
-      <c r="AP1" t="s" s="1">
-        <v>77</v>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>20</v>
@@ -1970,45 +1607,39 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" hidden="true">
+      <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="B3" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2016,31 +1647,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2090,13 +1721,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2116,19 +1747,13 @@
       <c r="AN3" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP3" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2136,10 +1761,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2148,16 +1773,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2208,19 +1833,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2234,19 +1859,13 @@
       <c r="AN4" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP4" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2254,31 +1873,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2328,19 +1947,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2354,19 +1973,13 @@
       <c r="AN5" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="AO5" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP5" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2374,10 +1987,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2389,16 +2002,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2424,80 +2037,74 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP6" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2509,16 +2116,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2568,19 +2175,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2589,35 +2196,29 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2629,16 +2230,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2688,13 +2289,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2709,35 +2310,29 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2749,17 +2344,15 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
@@ -2796,31 +2389,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2832,57 +2423,49 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -2930,19 +2513,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2954,54 +2537,50 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3050,56 +2629,50 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AP11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3108,20 +2681,22 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3170,56 +2745,50 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3228,20 +2797,18 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3290,45 +2857,39 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3336,35 +2897,33 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3388,13 +2947,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3412,45 +2971,39 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3458,35 +3011,33 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3510,13 +3061,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3534,22 +3085,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3558,32 +3109,26 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3592,22 +3137,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3632,11 +3175,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3654,81 +3199,71 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3776,45 +3311,39 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3822,10 +3351,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3834,21 +3363,23 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3896,19 +3427,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3917,35 +3448,29 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3954,22 +3479,20 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4018,81 +3541,73 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4116,13 +3631,11 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4140,45 +3653,39 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4186,10 +3693,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4198,21 +3705,23 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4236,13 +3745,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4260,19 +3769,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4281,24 +3790,18 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4306,10 +3809,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4318,20 +3821,20 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4380,45 +3883,39 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4426,10 +3923,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4438,22 +3935,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4502,45 +3999,39 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4548,10 +4039,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4560,27 +4051,29 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4600,13 +4093,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4624,19 +4117,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4645,35 +4138,29 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4682,23 +4169,19 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4722,13 +4205,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4746,45 +4229,39 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4792,10 +4269,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4804,23 +4281,21 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4844,13 +4319,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4868,45 +4343,39 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4914,10 +4383,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4926,20 +4395,18 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4964,13 +4431,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4988,45 +4455,39 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>316</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5034,10 +4495,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5049,20 +4510,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5086,13 +4543,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5110,45 +4567,39 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5156,10 +4607,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5171,17 +4622,15 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5230,45 +4679,39 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5276,10 +4719,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5291,17 +4734,15 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5350,56 +4791,50 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5411,20 +4846,18 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>345</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5472,19 +4905,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>350</v>
+        <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5493,56 +4926,54 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>354</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5590,19 +5021,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5611,35 +5042,29 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5651,17 +5076,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>138</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5686,13 +5109,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5710,19 +5133,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5731,60 +5154,50 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5808,13 +5221,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5832,19 +5245,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5853,24 +5266,18 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5878,10 +5285,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5893,13 +5300,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>369</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>370</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5950,19 +5357,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5971,24 +5378,18 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5996,10 +5397,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6011,16 +5412,18 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>368</v>
+        <v>307</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6068,19 +5471,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6089,24 +5492,18 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>372</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6114,10 +5511,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6129,20 +5526,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6166,13 +5559,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>383</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6190,1732 +5583,52 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>386</v>
+        <v>271</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN37">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI36">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>